--- a/datos_nino_mensual.xlsx
+++ b/datos_nino_mensual.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://intaarg-my.sharepoint.com/personal/lewczuk_nuria_inta_gob_ar/Documents/shiny_app/app_EMCBalcarce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="396" documentId="8_{D6F50C59-027A-4885-8A20-DA8410D8D698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F999E95B-EEEB-4450-BA2F-2B6E6D2E5CA2}"/>
+  <xr:revisionPtr revIDLastSave="404" documentId="8_{D6F50C59-027A-4885-8A20-DA8410D8D698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63DA2B1F-7887-480E-94D3-124B45D33CB1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8120B771-92F1-4794-9EFD-C5F0B4C6029F}"/>
+    <workbookView xWindow="-20610" yWindow="4575" windowWidth="20730" windowHeight="11040" xr2:uid="{8120B771-92F1-4794-9EFD-C5F0B4C6029F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -410,7 +410,18 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2915E338-8BAB-410F-8D2B-2FCCE170B7B1}" name="Tabla1" displayName="Tabla1" ref="A1:O433" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="A1:O433" xr:uid="{2915E338-8BAB-410F-8D2B-2FCCE170B7B1}"/>
+  <autoFilter ref="A1:O433" xr:uid="{2915E338-8BAB-410F-8D2B-2FCCE170B7B1}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Balcarce"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Julio"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{8D58C604-7B9B-4E56-AE4E-E53465BD2FCA}" name="Año"/>
     <tableColumn id="2" xr3:uid="{8ED663FD-F228-4716-B726-5F338E03DD57}" name="Localidad"/>
@@ -757,7 +768,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2452F3-4462-4A06-9EC7-8F74EFD1358E}">
-  <dimension ref="A1:O433"/>
+  <dimension ref="A1:O436"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
@@ -822,7 +833,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1982</v>
       </c>
@@ -873,7 +884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1987</v>
       </c>
@@ -924,7 +935,7 @@
         <v>44.444444444444443</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1991</v>
       </c>
@@ -975,7 +986,7 @@
         <v>261.11111111111114</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1994</v>
       </c>
@@ -1026,7 +1037,7 @@
         <v>13.888888888888889</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1997</v>
       </c>
@@ -1077,7 +1088,7 @@
         <v>186.11111111111111</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2002</v>
       </c>
@@ -1128,7 +1139,7 @@
         <v>-83.333333333333343</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2004</v>
       </c>
@@ -1179,7 +1190,7 @@
         <v>5.5555555555555554</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2015</v>
       </c>
@@ -1230,7 +1241,7 @@
         <v>-30.555555555555557</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2023</v>
       </c>
@@ -1740,7 +1751,7 @@
         <v>79.411764705882348</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1982</v>
       </c>
@@ -1791,7 +1802,7 @@
         <v>-81.081081081081081</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1987</v>
       </c>
@@ -1842,7 +1853,7 @@
         <v>16.216216216216218</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1991</v>
       </c>
@@ -1893,7 +1904,7 @@
         <v>-3.3333333333333335</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1994</v>
       </c>
@@ -1944,7 +1955,7 @@
         <v>-26.666666666666668</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1997</v>
       </c>
@@ -1995,7 +2006,7 @@
         <v>123.33333333333334</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2002</v>
       </c>
@@ -2046,7 +2057,7 @@
         <v>313.33333333333331</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2004</v>
       </c>
@@ -2097,7 +2108,7 @@
         <v>273.33333333333331</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2015</v>
       </c>
@@ -2148,7 +2159,7 @@
         <v>296.66666666666669</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2023</v>
       </c>
@@ -2199,7 +2210,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1982</v>
       </c>
@@ -2250,7 +2261,7 @@
         <v>127.45098039215685</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>1987</v>
       </c>
@@ -2301,7 +2312,7 @@
         <v>-45.098039215686278</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>1991</v>
       </c>
@@ -2352,7 +2363,7 @@
         <v>15.254237288135593</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>1994</v>
       </c>
@@ -2403,7 +2414,7 @@
         <v>-22.033898305084744</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>1997</v>
       </c>
@@ -2454,7 +2465,7 @@
         <v>-74.576271186440678</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2002</v>
       </c>
@@ -2505,7 +2516,7 @@
         <v>50.847457627118644</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2004</v>
       </c>
@@ -2556,7 +2567,7 @@
         <v>-71.186440677966104</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2015</v>
       </c>
@@ -2607,7 +2618,7 @@
         <v>-83.050847457627114</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2023</v>
       </c>
@@ -2658,7 +2669,7 @@
         <v>-33.898305084745758</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>1982</v>
       </c>
@@ -2709,7 +2720,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>1987</v>
       </c>
@@ -2760,7 +2771,7 @@
         <v>-7.5</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>1991</v>
       </c>
@@ -2811,7 +2822,7 @@
         <v>-30.76923076923077</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1994</v>
       </c>
@@ -2862,7 +2873,7 @@
         <v>65.384615384615387</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>1997</v>
       </c>
@@ -2913,7 +2924,7 @@
         <v>196.15384615384613</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2002</v>
       </c>
@@ -2964,7 +2975,7 @@
         <v>110.25641025641026</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2004</v>
       </c>
@@ -3015,7 +3026,7 @@
         <v>-15.384615384615385</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2015</v>
       </c>
@@ -3066,7 +3077,7 @@
         <v>15.384615384615385</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2023</v>
       </c>
@@ -3117,7 +3128,7 @@
         <v>7.6923076923076925</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>1982</v>
       </c>
@@ -3168,7 +3179,7 @@
         <v>-18.75</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>1987</v>
       </c>
@@ -3219,7 +3230,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>1991</v>
       </c>
@@ -3270,7 +3281,7 @@
         <v>4.1666666666666661</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>1994</v>
       </c>
@@ -3321,7 +3332,7 @@
         <v>9.375</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>1997</v>
       </c>
@@ -3372,7 +3383,7 @@
         <v>-16.666666666666664</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2002</v>
       </c>
@@ -3423,7 +3434,7 @@
         <v>90.625</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2004</v>
       </c>
@@ -3474,7 +3485,7 @@
         <v>15.625</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2015</v>
       </c>
@@ -3525,7 +3536,7 @@
         <v>-20.833333333333336</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2023</v>
       </c>
@@ -3576,7 +3587,7 @@
         <v>60.416666666666664</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>1982</v>
       </c>
@@ -3627,7 +3638,7 @@
         <v>-37.349397590361441</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>1987</v>
       </c>
@@ -3678,7 +3689,7 @@
         <v>33.734939759036145</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>1991</v>
       </c>
@@ -3729,7 +3740,7 @@
         <v>122.85714285714286</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>1994</v>
       </c>
@@ -3780,7 +3791,7 @@
         <v>75.714285714285708</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>1997</v>
       </c>
@@ -3831,7 +3842,7 @@
         <v>44.285714285714285</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2002</v>
       </c>
@@ -3882,7 +3893,7 @@
         <v>12.857142857142856</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2004</v>
       </c>
@@ -3933,7 +3944,7 @@
         <v>54.285714285714285</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2015</v>
       </c>
@@ -3984,7 +3995,7 @@
         <v>-48.571428571428569</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2023</v>
       </c>
@@ -4035,7 +4046,7 @@
         <v>291.42857142857139</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>1982</v>
       </c>
@@ -4086,7 +4097,7 @@
         <v>-44.444444444444443</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>1987</v>
       </c>
@@ -4137,7 +4148,7 @@
         <v>62.698412698412696</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>1991</v>
       </c>
@@ -4188,7 +4199,7 @@
         <v>40.196078431372548</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>1994</v>
       </c>
@@ -4239,7 +4250,7 @@
         <v>-38.235294117647058</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>1997</v>
       </c>
@@ -4290,7 +4301,7 @@
         <v>82.35294117647058</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2002</v>
       </c>
@@ -4341,7 +4352,7 @@
         <v>-47.058823529411761</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2004</v>
       </c>
@@ -4392,7 +4403,7 @@
         <v>-47.058823529411761</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2015</v>
       </c>
@@ -4443,7 +4454,7 @@
         <v>-41.17647058823529</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2023</v>
       </c>
@@ -4494,7 +4505,7 @@
         <v>-61.764705882352942</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>1982</v>
       </c>
@@ -4545,7 +4556,7 @@
         <v>-33.734939759036145</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>1987</v>
       </c>
@@ -4596,7 +4607,7 @@
         <v>28.915662650602407</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>1991</v>
       </c>
@@ -4647,7 +4658,7 @@
         <v>140.69767441860466</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>1994</v>
       </c>
@@ -4698,7 +4709,7 @@
         <v>-10.465116279069768</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>1997</v>
       </c>
@@ -4749,7 +4760,7 @@
         <v>-8.1395348837209305</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2002</v>
       </c>
@@ -4800,7 +4811,7 @@
         <v>27.906976744186046</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2004</v>
       </c>
@@ -4851,7 +4862,7 @@
         <v>30.232558139534881</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>2015</v>
       </c>
@@ -4902,7 +4913,7 @@
         <v>141.86046511627907</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>2023</v>
       </c>
@@ -4953,7 +4964,7 @@
         <v>66.279069767441854</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>1982</v>
       </c>
@@ -5004,7 +5015,7 @@
         <v>148.83720930232559</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>1987</v>
       </c>
@@ -5055,7 +5066,7 @@
         <v>-46.511627906976742</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>1991</v>
       </c>
@@ -5106,7 +5117,7 @@
         <v>139.65517241379311</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>1994</v>
       </c>
@@ -5157,7 +5168,7 @@
         <v>43.103448275862064</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>1997</v>
       </c>
@@ -5208,7 +5219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>2002</v>
       </c>
@@ -5259,7 +5270,7 @@
         <v>-68.965517241379317</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>2004</v>
       </c>
@@ -5310,7 +5321,7 @@
         <v>-48.275862068965516</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>2015</v>
       </c>
@@ -5361,7 +5372,7 @@
         <v>-36.206896551724135</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>2023</v>
       </c>
@@ -5412,7 +5423,7 @@
         <v>-37.931034482758619</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>1982</v>
       </c>
@@ -5463,7 +5474,7 @@
         <v>148.88888888888889</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>1987</v>
       </c>
@@ -5514,7 +5525,7 @@
         <v>171.11111111111111</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>1991</v>
       </c>
@@ -5565,7 +5576,7 @@
         <v>-16.666666666666664</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>1994</v>
       </c>
@@ -5616,7 +5627,7 @@
         <v>1.6666666666666667</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>1997</v>
       </c>
@@ -5667,7 +5678,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>2002</v>
       </c>
@@ -5718,7 +5729,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>2004</v>
       </c>
@@ -5769,7 +5780,7 @@
         <v>33.333333333333329</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>2015</v>
       </c>
@@ -5820,7 +5831,7 @@
         <v>36.666666666666664</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>2023</v>
       </c>
@@ -5871,7 +5882,7 @@
         <v>171.66666666666666</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>1982</v>
       </c>
@@ -5922,7 +5933,7 @@
         <v>-30.952380952380953</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>1987</v>
       </c>
@@ -5973,7 +5984,7 @@
         <v>40.476190476190474</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>1991</v>
       </c>
@@ -6024,7 +6035,7 @@
         <v>-67.346938775510196</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>1994</v>
       </c>
@@ -6075,7 +6086,7 @@
         <v>-77.551020408163268</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>1997</v>
       </c>
@@ -6126,7 +6137,7 @@
         <v>69.387755102040813</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>2002</v>
       </c>
@@ -6177,7 +6188,7 @@
         <v>79.591836734693871</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>2004</v>
       </c>
@@ -6228,7 +6239,7 @@
         <v>112.24489795918366</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>2015</v>
       </c>
@@ -6279,7 +6290,7 @@
         <v>202.0408163265306</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>2023</v>
       </c>
@@ -6330,7 +6341,7 @@
         <v>-24.489795918367346</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>1982</v>
       </c>
@@ -6381,7 +6392,7 @@
         <v>163.15789473684211</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>1987</v>
       </c>
@@ -6432,7 +6443,7 @@
         <v>-26.315789473684209</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>1991</v>
       </c>
@@ -6483,7 +6494,7 @@
         <v>28.571428571428569</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>1994</v>
       </c>
@@ -6534,7 +6545,7 @@
         <v>33.928571428571431</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>1997</v>
       </c>
@@ -6585,7 +6596,7 @@
         <v>-32.142857142857146</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>2002</v>
       </c>
@@ -6636,7 +6647,7 @@
         <v>116.07142857142858</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>2004</v>
       </c>
@@ -6687,7 +6698,7 @@
         <v>-39.285714285714285</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>2015</v>
       </c>
@@ -6738,7 +6749,7 @@
         <v>-78.571428571428569</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>2023</v>
       </c>
@@ -6789,7 +6800,7 @@
         <v>-37.5</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>1982</v>
       </c>
@@ -6840,7 +6851,7 @@
         <v>55.000000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>1987</v>
       </c>
@@ -6891,7 +6902,7 @@
         <v>57.499999999999993</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>1991</v>
       </c>
@@ -6942,7 +6953,7 @@
         <v>161.11111111111111</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>1994</v>
       </c>
@@ -6993,7 +7004,7 @@
         <v>120.83333333333333</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>1997</v>
       </c>
@@ -7044,7 +7055,7 @@
         <v>8.3333333333333321</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>2002</v>
       </c>
@@ -7095,7 +7106,7 @@
         <v>281.94444444444446</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>2004</v>
       </c>
@@ -7146,7 +7157,7 @@
         <v>-30.555555555555557</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>2015</v>
       </c>
@@ -7197,7 +7208,7 @@
         <v>31.944444444444443</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>2023</v>
       </c>
@@ -7248,7 +7259,7 @@
         <v>-72.222222222222214</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>1982</v>
       </c>
@@ -7299,7 +7310,7 @@
         <v>-11.267605633802818</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>1987</v>
       </c>
@@ -7350,7 +7361,7 @@
         <v>-56.338028169014088</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>1991</v>
       </c>
@@ -7401,7 +7412,7 @@
         <v>-37.5</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>1994</v>
       </c>
@@ -7452,7 +7463,7 @@
         <v>-73.611111111111114</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>1997</v>
       </c>
@@ -7503,7 +7514,7 @@
         <v>101.38888888888889</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>2002</v>
       </c>
@@ -7554,7 +7565,7 @@
         <v>2.7777777777777777</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>2004</v>
       </c>
@@ -7605,7 +7616,7 @@
         <v>4.1666666666666661</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>2015</v>
       </c>
@@ -7656,7 +7667,7 @@
         <v>-25</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>2023</v>
       </c>
@@ -7707,7 +7718,7 @@
         <v>-8.3333333333333321</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>1982</v>
       </c>
@@ -7758,7 +7769,7 @@
         <v>23.711340206185564</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>1987</v>
       </c>
@@ -7809,7 +7820,7 @@
         <v>35.051546391752574</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>1991</v>
       </c>
@@ -7860,7 +7871,7 @@
         <v>-4.4444444444444446</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>1994</v>
       </c>
@@ -7911,7 +7922,7 @@
         <v>1.1111111111111112</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>1997</v>
       </c>
@@ -7962,7 +7973,7 @@
         <v>43.333333333333336</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>2002</v>
       </c>
@@ -8013,7 +8024,7 @@
         <v>-37.777777777777779</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>2004</v>
       </c>
@@ -8064,7 +8075,7 @@
         <v>-36.666666666666664</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>2015</v>
       </c>
@@ -8115,7 +8126,7 @@
         <v>-85.555555555555557</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>2023</v>
       </c>
@@ -8166,7 +8177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>1982</v>
       </c>
@@ -8217,7 +8228,7 @@
         <v>56.730769230769226</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>1987</v>
       </c>
@@ -8268,7 +8279,7 @@
         <v>-19.230769230769234</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>1991</v>
       </c>
@@ -8319,7 +8330,7 @@
         <v>16.483516483516482</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>1994</v>
       </c>
@@ -8370,7 +8381,7 @@
         <v>39.560439560439562</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>1997</v>
       </c>
@@ -8421,7 +8432,7 @@
         <v>9.8901098901098905</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>2002</v>
       </c>
@@ -8472,7 +8483,7 @@
         <v>9.8901098901098905</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>2004</v>
       </c>
@@ -8523,7 +8534,7 @@
         <v>-16.483516483516482</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>2015</v>
       </c>
@@ -8574,7 +8585,7 @@
         <v>131.86813186813185</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>2023</v>
       </c>
@@ -8625,7 +8636,7 @@
         <v>-57.142857142857139</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>1982</v>
       </c>
@@ -8676,7 +8687,7 @@
         <v>-68.571428571428569</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>1987</v>
       </c>
@@ -8727,7 +8738,7 @@
         <v>-54.285714285714285</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>1991</v>
       </c>
@@ -8778,7 +8789,7 @@
         <v>215.11627906976742</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>1994</v>
       </c>
@@ -8829,7 +8840,7 @@
         <v>-18.604651162790699</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>1997</v>
       </c>
@@ -8880,7 +8891,7 @@
         <v>-45.348837209302324</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>2002</v>
       </c>
@@ -8931,7 +8942,7 @@
         <v>-11.627906976744185</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>2004</v>
       </c>
@@ -8982,7 +8993,7 @@
         <v>43.02325581395349</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>2015</v>
       </c>
@@ -9033,7 +9044,7 @@
         <v>96.511627906976756</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>2023</v>
       </c>
@@ -9084,7 +9095,7 @@
         <v>32.558139534883722</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>1982</v>
       </c>
@@ -9135,7 +9146,7 @@
         <v>53.125</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>1987</v>
       </c>
@@ -9186,7 +9197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>1991</v>
       </c>
@@ -9237,7 +9248,7 @@
         <v>275.67567567567568</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>1994</v>
       </c>
@@ -9288,7 +9299,7 @@
         <v>-2.7027027027027026</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>1997</v>
       </c>
@@ -9339,7 +9350,7 @@
         <v>135.13513513513513</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>2002</v>
       </c>
@@ -9390,7 +9401,7 @@
         <v>-83.78378378378379</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>2004</v>
       </c>
@@ -9441,7 +9452,7 @@
         <v>-18.918918918918919</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>2015</v>
       </c>
@@ -9492,7 +9503,7 @@
         <v>5.4054054054054053</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>2023</v>
       </c>
@@ -9543,7 +9554,7 @@
         <v>-2.7027027027027026</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>1982</v>
       </c>
@@ -9594,7 +9605,7 @@
         <v>37.931034482758619</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>1987</v>
       </c>
@@ -9645,7 +9656,7 @@
         <v>272.41379310344826</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>1991</v>
       </c>
@@ -9696,7 +9707,7 @@
         <v>-63.888888888888886</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>1994</v>
       </c>
@@ -9747,7 +9758,7 @@
         <v>69.444444444444443</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>1997</v>
       </c>
@@ -9798,7 +9809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>2002</v>
       </c>
@@ -9849,7 +9860,7 @@
         <v>33.333333333333329</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>2004</v>
       </c>
@@ -9900,7 +9911,7 @@
         <v>172.22222222222223</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>2015</v>
       </c>
@@ -9951,7 +9962,7 @@
         <v>69.444444444444443</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>2023</v>
       </c>
@@ -10002,7 +10013,7 @@
         <v>47.222222222222221</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>1982</v>
       </c>
@@ -10053,7 +10064,7 @@
         <v>-64.705882352941174</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>1987</v>
       </c>
@@ -10104,7 +10115,7 @@
         <v>2.9411764705882351</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>1991</v>
       </c>
@@ -10155,7 +10166,7 @@
         <v>-64.705882352941174</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>1994</v>
       </c>
@@ -10206,7 +10217,7 @@
         <v>-41.17647058823529</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>1997</v>
       </c>
@@ -10257,7 +10268,7 @@
         <v>158.8235294117647</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>2002</v>
       </c>
@@ -10308,7 +10319,7 @@
         <v>185.29411764705884</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>2004</v>
       </c>
@@ -10359,7 +10370,7 @@
         <v>147.05882352941177</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>2015</v>
       </c>
@@ -10410,7 +10421,7 @@
         <v>352.94117647058823</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>2023</v>
       </c>
@@ -10461,7 +10472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>1982</v>
       </c>
@@ -10512,7 +10523,7 @@
         <v>152.38095238095238</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>1987</v>
       </c>
@@ -10563,7 +10574,7 @@
         <v>-57.142857142857139</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>1991</v>
       </c>
@@ -10614,7 +10625,7 @@
         <v>46.938775510204081</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>1994</v>
       </c>
@@ -10665,7 +10676,7 @@
         <v>-18.367346938775512</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>1997</v>
       </c>
@@ -10716,7 +10727,7 @@
         <v>-36.734693877551024</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>2002</v>
       </c>
@@ -10767,7 +10778,7 @@
         <v>77.551020408163268</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>2004</v>
       </c>
@@ -10818,7 +10829,7 @@
         <v>-42.857142857142854</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>2015</v>
       </c>
@@ -10869,7 +10880,7 @@
         <v>-79.591836734693871</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>2023</v>
       </c>
@@ -10920,7 +10931,7 @@
         <v>30.612244897959183</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>1982</v>
       </c>
@@ -10971,7 +10982,7 @@
         <v>52.12765957446809</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>1987</v>
       </c>
@@ -11022,7 +11033,7 @@
         <v>4.2553191489361701</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>1991</v>
       </c>
@@ -11073,7 +11084,7 @@
         <v>39.189189189189186</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>1994</v>
       </c>
@@ -11124,7 +11135,7 @@
         <v>25.675675675675674</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>1997</v>
       </c>
@@ -11175,7 +11186,7 @@
         <v>248.64864864864865</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>2002</v>
       </c>
@@ -11226,7 +11237,7 @@
         <v>163.51351351351352</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>2004</v>
       </c>
@@ -11277,7 +11288,7 @@
         <v>-24.324324324324326</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>2015</v>
       </c>
@@ -11328,7 +11339,7 @@
         <v>9.4594594594594597</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>2023</v>
       </c>
@@ -11379,7 +11390,7 @@
         <v>13.513513513513514</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>1982</v>
       </c>
@@ -11430,7 +11441,7 @@
         <v>-17.567567567567568</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>1987</v>
       </c>
@@ -11481,7 +11492,7 @@
         <v>58.108108108108105</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>1991</v>
       </c>
@@ -11532,7 +11543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>1994</v>
       </c>
@@ -11583,7 +11594,7 @@
         <v>-71.910112359550567</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>1997</v>
       </c>
@@ -11634,7 +11645,7 @@
         <v>-26.966292134831459</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>2002</v>
       </c>
@@ -11685,7 +11696,7 @@
         <v>79.775280898876403</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>2004</v>
       </c>
@@ -11736,7 +11747,7 @@
         <v>-40.449438202247187</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>2015</v>
       </c>
@@ -11787,7 +11798,7 @@
         <v>64.044943820224717</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>2023</v>
       </c>
@@ -11838,7 +11849,7 @@
         <v>65.168539325842701</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>1982</v>
       </c>
@@ -11889,7 +11900,7 @@
         <v>83.82352941176471</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>1987</v>
       </c>
@@ -11940,7 +11951,7 @@
         <v>36.764705882352942</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>1991</v>
       </c>
@@ -11991,7 +12002,7 @@
         <v>93.333333333333329</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>1994</v>
       </c>
@@ -12042,7 +12053,7 @@
         <v>133.33333333333331</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>1997</v>
       </c>
@@ -12093,7 +12104,7 @@
         <v>55.000000000000007</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>2002</v>
       </c>
@@ -12144,7 +12155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>2004</v>
       </c>
@@ -12195,7 +12206,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>2015</v>
       </c>
@@ -12246,7 +12257,7 @@
         <v>-55.000000000000007</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>2023</v>
       </c>
@@ -12297,7 +12308,7 @@
         <v>301.66666666666669</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>1982</v>
       </c>
@@ -12348,7 +12359,7 @@
         <v>59.595959595959592</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>1987</v>
       </c>
@@ -12399,7 +12410,7 @@
         <v>16.161616161616163</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>1991</v>
       </c>
@@ -12450,7 +12461,7 @@
         <v>46.875</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>1994</v>
       </c>
@@ -12501,7 +12512,7 @@
         <v>-40.625</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>1997</v>
       </c>
@@ -12552,7 +12563,7 @@
         <v>68.75</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>2002</v>
       </c>
@@ -12603,7 +12614,7 @@
         <v>-15.625</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>2004</v>
       </c>
@@ -12654,7 +12665,7 @@
         <v>-62.5</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>2015</v>
       </c>
@@ -12705,7 +12716,7 @@
         <v>77.083333333333343</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>2023</v>
       </c>
@@ -12756,7 +12767,7 @@
         <v>-48.958333333333329</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>1982</v>
       </c>
@@ -12807,7 +12818,7 @@
         <v>59.210526315789465</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>1987</v>
       </c>
@@ -12858,7 +12869,7 @@
         <v>-9.2105263157894726</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>1991</v>
       </c>
@@ -12909,7 +12920,7 @@
         <v>55.102040816326522</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>1994</v>
       </c>
@@ -12960,7 +12971,7 @@
         <v>-22.448979591836736</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>1997</v>
       </c>
@@ -13011,7 +13022,7 @@
         <v>-55.102040816326522</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>2002</v>
       </c>
@@ -13062,7 +13073,7 @@
         <v>17.346938775510203</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>2004</v>
       </c>
@@ -13113,7 +13124,7 @@
         <v>51.020408163265309</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>2015</v>
       </c>
@@ -13164,7 +13175,7 @@
         <v>124.48979591836735</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>2023</v>
       </c>
@@ -13215,7 +13226,7 @@
         <v>40.816326530612244</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>1987</v>
       </c>
@@ -13266,7 +13277,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>1991</v>
       </c>
@@ -13317,7 +13328,7 @@
         <v>448.27586206896547</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>1994</v>
       </c>
@@ -13368,7 +13379,7 @@
         <v>-37.931034482758619</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>1997</v>
       </c>
@@ -13419,7 +13430,7 @@
         <v>189.65517241379311</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>2002</v>
       </c>
@@ -13470,7 +13481,7 @@
         <v>-86.206896551724128</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>2004</v>
       </c>
@@ -13521,7 +13532,7 @@
         <v>-3.4482758620689653</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>2015</v>
       </c>
@@ -13572,7 +13583,7 @@
         <v>20.689655172413794</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>2023</v>
       </c>
@@ -13623,7 +13634,7 @@
         <v>10.344827586206897</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>1987</v>
       </c>
@@ -13674,7 +13685,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>1991</v>
       </c>
@@ -13725,7 +13736,7 @@
         <v>-65.625</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>1994</v>
       </c>
@@ -13776,7 +13787,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>1997</v>
       </c>
@@ -13827,7 +13838,7 @@
         <v>-18.75</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>2002</v>
       </c>
@@ -13878,7 +13889,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>2004</v>
       </c>
@@ -13929,7 +13940,7 @@
         <v>131.25</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>2015</v>
       </c>
@@ -13980,7 +13991,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>2023</v>
       </c>
@@ -14031,7 +14042,7 @@
         <v>203.125</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>1987</v>
       </c>
@@ -14082,7 +14093,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>1991</v>
       </c>
@@ -14133,7 +14144,7 @@
         <v>-53.125</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>1994</v>
       </c>
@@ -14184,7 +14195,7 @@
         <v>-37.5</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>1997</v>
       </c>
@@ -14235,7 +14246,7 @@
         <v>68.75</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>2002</v>
       </c>
@@ -14286,7 +14297,7 @@
         <v>271.875</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>2004</v>
       </c>
@@ -14337,7 +14348,7 @@
         <v>93.75</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>2015</v>
       </c>
@@ -14388,7 +14399,7 @@
         <v>296.875</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>2023</v>
       </c>
@@ -14439,7 +14450,7 @@
         <v>-21.875</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>1987</v>
       </c>
@@ -14490,7 +14501,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>1991</v>
       </c>
@@ -14541,7 +14552,7 @@
         <v>45.454545454545453</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>1994</v>
       </c>
@@ -14592,7 +14603,7 @@
         <v>-67.272727272727266</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>1997</v>
       </c>
@@ -14643,7 +14654,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>2002</v>
       </c>
@@ -14694,7 +14705,7 @@
         <v>25.454545454545453</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>2004</v>
       </c>
@@ -14745,7 +14756,7 @@
         <v>-63.636363636363633</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>2015</v>
       </c>
@@ -14796,7 +14807,7 @@
         <v>-85.454545454545453</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>2023</v>
       </c>
@@ -14847,7 +14858,7 @@
         <v>38.181818181818187</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>1987</v>
       </c>
@@ -14898,7 +14909,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>1991</v>
       </c>
@@ -14949,7 +14960,7 @@
         <v>-12.5</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>1994</v>
       </c>
@@ -15000,7 +15011,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>1997</v>
       </c>
@@ -15051,7 +15062,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>2002</v>
       </c>
@@ -15102,7 +15113,7 @@
         <v>86.25</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>2004</v>
       </c>
@@ -15153,7 +15164,7 @@
         <v>-2.5</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>2015</v>
       </c>
@@ -15204,7 +15215,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>2023</v>
       </c>
@@ -15255,7 +15266,7 @@
         <v>41.25</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>1987</v>
       </c>
@@ -15306,7 +15317,7 @@
         <v>27.173913043478258</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>1991</v>
       </c>
@@ -15357,7 +15368,7 @@
         <v>32.53012048192771</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>1994</v>
       </c>
@@ -15408,7 +15419,7 @@
         <v>-50.602409638554214</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>1997</v>
       </c>
@@ -15459,7 +15470,7 @@
         <v>-14.457831325301203</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>2002</v>
       </c>
@@ -15510,7 +15521,7 @@
         <v>68.674698795180717</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>2004</v>
       </c>
@@ -15561,7 +15572,7 @@
         <v>-13.253012048192772</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>2015</v>
       </c>
@@ -15612,7 +15623,7 @@
         <v>-57.831325301204814</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>2023</v>
       </c>
@@ -15663,7 +15674,7 @@
         <v>77.108433734939766</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>1987</v>
       </c>
@@ -15714,7 +15725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>1991</v>
       </c>
@@ -15765,7 +15776,7 @@
         <v>213.55932203389833</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>1994</v>
       </c>
@@ -15816,7 +15827,7 @@
         <v>154.23728813559322</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>1997</v>
       </c>
@@ -15867,7 +15878,7 @@
         <v>11.864406779661017</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>2002</v>
       </c>
@@ -15918,7 +15929,7 @@
         <v>-5.0847457627118651</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>2004</v>
       </c>
@@ -15969,7 +15980,7 @@
         <v>86.440677966101703</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>2015</v>
       </c>
@@ -16020,7 +16031,7 @@
         <v>-11.864406779661017</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>2023</v>
       </c>
@@ -16071,7 +16082,7 @@
         <v>374.57627118644064</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>1987</v>
       </c>
@@ -16122,7 +16133,7 @@
         <v>-5</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>1991</v>
       </c>
@@ -16173,7 +16184,7 @@
         <v>129.34782608695653</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>1994</v>
       </c>
@@ -16224,7 +16235,7 @@
         <v>-38.04347826086957</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>1997</v>
       </c>
@@ -16275,7 +16286,7 @@
         <v>164.13043478260869</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>2002</v>
       </c>
@@ -16326,7 +16337,7 @@
         <v>-34.782608695652172</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>2004</v>
       </c>
@@ -16377,7 +16388,7 @@
         <v>-33.695652173913047</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>2015</v>
       </c>
@@ -16428,7 +16439,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>2023</v>
       </c>
@@ -16479,7 +16490,7 @@
         <v>-86.956521739130437</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>1987</v>
       </c>
@@ -16530,7 +16541,7 @@
         <v>-20.689655172413794</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>1991</v>
       </c>
@@ -16581,7 +16592,7 @@
         <v>196.62921348314606</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>1994</v>
       </c>
@@ -16632,7 +16643,7 @@
         <v>-58.426966292134829</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>1997</v>
       </c>
@@ -16683,7 +16694,7 @@
         <v>14.606741573033707</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>2002</v>
       </c>
@@ -16734,7 +16745,7 @@
         <v>-6.7415730337078648</v>
       </c>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>2004</v>
       </c>
@@ -16785,7 +16796,7 @@
         <v>23.595505617977526</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>2015</v>
       </c>
@@ -16836,7 +16847,7 @@
         <v>85.393258426966284</v>
       </c>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>2023</v>
       </c>
@@ -16887,7 +16898,7 @@
         <v>70.786516853932582</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>1982</v>
       </c>
@@ -16938,7 +16949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>1987</v>
       </c>
@@ -16989,7 +17000,7 @@
         <v>44.444444444444443</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>1991</v>
       </c>
@@ -17040,7 +17051,7 @@
         <v>261.11111111111114</v>
       </c>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>1994</v>
       </c>
@@ -17091,7 +17102,7 @@
         <v>13.888888888888889</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>1997</v>
       </c>
@@ -17142,7 +17153,7 @@
         <v>186.11111111111111</v>
       </c>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>2002</v>
       </c>
@@ -17193,7 +17204,7 @@
         <v>-83.333333333333343</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>2004</v>
       </c>
@@ -17244,7 +17255,7 @@
         <v>5.5555555555555554</v>
       </c>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>2015</v>
       </c>
@@ -17295,7 +17306,7 @@
         <v>-30.555555555555557</v>
       </c>
     </row>
-    <row r="325" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:15" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>2023</v>
       </c>
@@ -17346,7 +17357,7 @@
         <v>-36.111111111111107</v>
       </c>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>1982</v>
       </c>
@@ -17397,7 +17408,7 @@
         <v>-20</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>1987</v>
       </c>
@@ -17448,7 +17459,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>1991</v>
       </c>
@@ -17499,7 +17510,7 @@
         <v>-47.058823529411761</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>1994</v>
       </c>
@@ -17550,7 +17561,7 @@
         <v>-55.882352941176471</v>
       </c>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>1997</v>
       </c>
@@ -17601,7 +17612,7 @@
         <v>29.411764705882355</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>2002</v>
       </c>
@@ -17652,7 +17663,7 @@
         <v>82.35294117647058</v>
       </c>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>2004</v>
       </c>
@@ -17703,7 +17714,7 @@
         <v>129.41176470588235</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>2015</v>
       </c>
@@ -17754,7 +17765,7 @@
         <v>52.941176470588239</v>
       </c>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>2023</v>
       </c>
@@ -17805,7 +17816,7 @@
         <v>79.411764705882348</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>1982</v>
       </c>
@@ -17856,7 +17867,7 @@
         <v>-81.081081081081081</v>
       </c>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>1987</v>
       </c>
@@ -17907,7 +17918,7 @@
         <v>16.216216216216218</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>1991</v>
       </c>
@@ -17958,7 +17969,7 @@
         <v>-3.3333333333333335</v>
       </c>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>1994</v>
       </c>
@@ -18009,7 +18020,7 @@
         <v>-26.666666666666668</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>1997</v>
       </c>
@@ -18060,7 +18071,7 @@
         <v>123.33333333333334</v>
       </c>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>2002</v>
       </c>
@@ -18111,7 +18122,7 @@
         <v>313.33333333333331</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>2004</v>
       </c>
@@ -18162,7 +18173,7 @@
         <v>273.33333333333331</v>
       </c>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>2015</v>
       </c>
@@ -18213,7 +18224,7 @@
         <v>296.66666666666669</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>2023</v>
       </c>
@@ -18264,7 +18275,7 @@
         <v>-30</v>
       </c>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>1982</v>
       </c>
@@ -18315,7 +18326,7 @@
         <v>127.45098039215685</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>1987</v>
       </c>
@@ -18366,7 +18377,7 @@
         <v>-45.098039215686278</v>
       </c>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>1991</v>
       </c>
@@ -18417,7 +18428,7 @@
         <v>15.254237288135593</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>1994</v>
       </c>
@@ -18468,7 +18479,7 @@
         <v>-22.033898305084744</v>
       </c>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>1997</v>
       </c>
@@ -18519,7 +18530,7 @@
         <v>-74.576271186440678</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>2002</v>
       </c>
@@ -18570,7 +18581,7 @@
         <v>50.847457627118644</v>
       </c>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>2004</v>
       </c>
@@ -18621,7 +18632,7 @@
         <v>-71.186440677966104</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>2015</v>
       </c>
@@ -18672,7 +18683,7 @@
         <v>-83.050847457627114</v>
       </c>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>2023</v>
       </c>
@@ -18723,7 +18734,7 @@
         <v>-33.898305084745758</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>1982</v>
       </c>
@@ -18774,7 +18785,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>1987</v>
       </c>
@@ -18825,7 +18836,7 @@
         <v>-7.5</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>1991</v>
       </c>
@@ -18876,7 +18887,7 @@
         <v>-30.76923076923077</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>1994</v>
       </c>
@@ -18927,7 +18938,7 @@
         <v>65.384615384615387</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>1997</v>
       </c>
@@ -18978,7 +18989,7 @@
         <v>196.15384615384613</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>2002</v>
       </c>
@@ -19029,7 +19040,7 @@
         <v>110.25641025641026</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>2004</v>
       </c>
@@ -19080,7 +19091,7 @@
         <v>-15.384615384615385</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>2015</v>
       </c>
@@ -19131,7 +19142,7 @@
         <v>15.384615384615385</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>2023</v>
       </c>
@@ -19182,7 +19193,7 @@
         <v>7.6923076923076925</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>1982</v>
       </c>
@@ -19233,7 +19244,7 @@
         <v>-18.75</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>1987</v>
       </c>
@@ -19284,7 +19295,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>1991</v>
       </c>
@@ -19335,7 +19346,7 @@
         <v>4.1666666666666661</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>1994</v>
       </c>
@@ -19386,7 +19397,7 @@
         <v>9.375</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>1997</v>
       </c>
@@ -19437,7 +19448,7 @@
         <v>-16.666666666666664</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>2002</v>
       </c>
@@ -19488,7 +19499,7 @@
         <v>90.625</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>2004</v>
       </c>
@@ -19539,7 +19550,7 @@
         <v>15.625</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>2015</v>
       </c>
@@ -19590,7 +19601,7 @@
         <v>-20.833333333333336</v>
       </c>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>2023</v>
       </c>
@@ -19641,7 +19652,7 @@
         <v>60.416666666666664</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>1982</v>
       </c>
@@ -19692,7 +19703,7 @@
         <v>-37.349397590361441</v>
       </c>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>1987</v>
       </c>
@@ -19743,7 +19754,7 @@
         <v>33.734939759036145</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>1991</v>
       </c>
@@ -19794,7 +19805,7 @@
         <v>122.85714285714286</v>
       </c>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>1994</v>
       </c>
@@ -19845,7 +19856,7 @@
         <v>75.714285714285708</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>1997</v>
       </c>
@@ -19896,7 +19907,7 @@
         <v>44.285714285714285</v>
       </c>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>2002</v>
       </c>
@@ -19947,7 +19958,7 @@
         <v>12.857142857142856</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>2004</v>
       </c>
@@ -19998,7 +20009,7 @@
         <v>54.285714285714285</v>
       </c>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>2015</v>
       </c>
@@ -20049,7 +20060,7 @@
         <v>-48.571428571428569</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>2023</v>
       </c>
@@ -20100,7 +20111,7 @@
         <v>291.42857142857139</v>
       </c>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>1982</v>
       </c>
@@ -20151,7 +20162,7 @@
         <v>-44.444444444444443</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>1987</v>
       </c>
@@ -20202,7 +20213,7 @@
         <v>62.698412698412696</v>
       </c>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>1991</v>
       </c>
@@ -20253,7 +20264,7 @@
         <v>40.196078431372548</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>1994</v>
       </c>
@@ -20304,7 +20315,7 @@
         <v>-38.235294117647058</v>
       </c>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>1997</v>
       </c>
@@ -20355,7 +20366,7 @@
         <v>82.35294117647058</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>2002</v>
       </c>
@@ -20406,7 +20417,7 @@
         <v>-47.058823529411761</v>
       </c>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>2004</v>
       </c>
@@ -20457,7 +20468,7 @@
         <v>-47.058823529411761</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>2015</v>
       </c>
@@ -20508,7 +20519,7 @@
         <v>-41.17647058823529</v>
       </c>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>2023</v>
       </c>
@@ -20559,7 +20570,7 @@
         <v>-61.764705882352942</v>
       </c>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>1982</v>
       </c>
@@ -20610,7 +20621,7 @@
         <v>-33.734939759036145</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>1987</v>
       </c>
@@ -20661,7 +20672,7 @@
         <v>28.915662650602407</v>
       </c>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>1991</v>
       </c>
@@ -20712,7 +20723,7 @@
         <v>140.69767441860466</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>1994</v>
       </c>
@@ -20763,7 +20774,7 @@
         <v>-10.465116279069768</v>
       </c>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>1997</v>
       </c>
@@ -20814,7 +20825,7 @@
         <v>-8.1395348837209305</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>2002</v>
       </c>
@@ -20865,7 +20876,7 @@
         <v>27.906976744186046</v>
       </c>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>2004</v>
       </c>
@@ -20916,7 +20927,7 @@
         <v>30.232558139534881</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>2015</v>
       </c>
@@ -20967,7 +20978,7 @@
         <v>141.86046511627907</v>
       </c>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>2023</v>
       </c>
@@ -21018,7 +21029,7 @@
         <v>66.279069767441854</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>2015</v>
       </c>
@@ -21071,7 +21082,7 @@
         <v>160.28985507246375</v>
       </c>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>2023</v>
       </c>
@@ -21124,7 +21135,7 @@
         <v>16.521739130434788</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>2015</v>
       </c>
@@ -21177,7 +21188,7 @@
         <v>-40.54054054054054</v>
       </c>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>2023</v>
       </c>
@@ -21230,7 +21241,7 @@
         <v>125.58558558558559</v>
       </c>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>2015</v>
       </c>
@@ -21283,7 +21294,7 @@
         <v>-99.011857707509876</v>
       </c>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>2023</v>
       </c>
@@ -21336,7 +21347,7 @@
         <v>-40.316205533596836</v>
       </c>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>2015</v>
       </c>
@@ -21389,7 +21400,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>2023</v>
       </c>
@@ -21442,7 +21453,7 @@
         <v>15.652173913043486</v>
       </c>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>2015</v>
       </c>
@@ -21495,7 +21506,7 @@
         <v>55.714285714285715</v>
       </c>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>2023</v>
       </c>
@@ -21548,7 +21559,7 @@
         <v>-2.2857142857142776</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>2015</v>
       </c>
@@ -21601,7 +21612,7 @@
         <v>-21.580547112462</v>
       </c>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>2023</v>
       </c>
@@ -21654,7 +21665,7 @@
         <v>2.735562310030391</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>2015</v>
       </c>
@@ -21707,7 +21718,7 @@
         <v>-63.992869875222823</v>
       </c>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>2023</v>
       </c>
@@ -21760,7 +21771,7 @@
         <v>55.971479500891263</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>2015</v>
       </c>
@@ -21813,7 +21824,7 @@
         <v>96.05263157894737</v>
       </c>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>2023</v>
       </c>
@@ -21866,7 +21877,7 @@
         <v>-75</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>2015</v>
       </c>
@@ -21919,7 +21930,7 @@
         <v>-50.127877237851656</v>
       </c>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>2023</v>
       </c>
@@ -21972,7 +21983,7 @@
         <v>40.664961636828636</v>
       </c>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>2015</v>
       </c>
@@ -22025,7 +22036,7 @@
         <v>871.75141242937855</v>
       </c>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>2023</v>
       </c>
@@ -22078,7 +22089,7 @@
         <v>134.4632768361582</v>
       </c>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>2015</v>
       </c>
@@ -22131,7 +22142,7 @@
         <v>-66.43518518518519</v>
       </c>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>2023</v>
       </c>
@@ -22184,7 +22195,7 @@
         <v>171.99074074074073</v>
       </c>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>2015</v>
       </c>
@@ -22237,7 +22248,7 @@
         <v>20.772946859903385</v>
       </c>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>2023</v>
       </c>
@@ -22290,7 +22301,7 @@
         <v>75.120772946859901</v>
       </c>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>2015</v>
       </c>
@@ -22343,7 +22354,7 @@
         <v>261.22448979591837</v>
       </c>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>2023</v>
       </c>
@@ -22389,7 +22400,7 @@
         <v>546.9387755102041</v>
       </c>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>2015</v>
       </c>
@@ -22442,7 +22453,7 @@
         <v>4.7058823529411766</v>
       </c>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>2023</v>
       </c>
@@ -22495,7 +22506,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>2015</v>
       </c>
@@ -22548,7 +22559,7 @@
         <v>130.26315789473685</v>
       </c>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>2023</v>
       </c>
@@ -22601,7 +22612,7 @@
         <v>57.894736842105253</v>
       </c>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>2015</v>
       </c>
@@ -22654,7 +22665,7 @@
         <v>151.98412698412699</v>
       </c>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>2023</v>
       </c>
@@ -22707,7 +22718,7 @@
         <v>161.9047619047619</v>
       </c>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>2015</v>
       </c>
@@ -22760,7 +22771,7 @@
         <v>44.100580270793024</v>
       </c>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>2023</v>
       </c>
@@ -22813,7 +22824,7 @@
         <v>-38.104448742746619</v>
       </c>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>2015</v>
       </c>
@@ -22866,7 +22877,7 @@
         <v>-34.508816120906808</v>
       </c>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>2023</v>
       </c>
@@ -22917,6 +22928,12 @@
       <c r="O433" s="13">
         <f>+(Tabla1[[#This Row],[Prec acum (mm)]]-Tabla1[[#This Row],[Prec acum (mm) historica]])/Tabla1[[#This Row],[Prec acum (mm) historica]]*100</f>
         <v>-13.098236775818645</v>
+      </c>
+    </row>
+    <row r="436" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="L436">
+        <f>+(K12-G12)/G12*100</f>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
